--- a/Project Outputs for MB_SAUVC26/ГИДР.123456.010-03.01/Документация/ГИДР.123456.011-03.01 ПЭ3.xlsx
+++ b/Project Outputs for MB_SAUVC26/ГИДР.123456.010-03.01/Документация/ГИДР.123456.011-03.01 ПЭ3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shustrik\AppData\Local\TempReleases\Snapshot\1\Assembly 01\Документация\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\AppData\Local\TempReleases\Snapshot\2\Assembly 01\Документация\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{996DB96E-3420-40A8-8E2E-066059FEEF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3445DF3F-2C31-4C2D-B5D6-D0AC2EC8EEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{5A40AB30-CFC6-4E4C-805C-79112E5FA8B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{6FDB28AC-23CF-4375-9627-FF36628DD5A4}"/>
   </bookViews>
   <sheets>
     <sheet name="ГИДР.123456.011-03.01 ПЭ3" sheetId="1" r:id="rId1"/>
@@ -23,21 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="121">
   <si>
     <t>Line #</t>
   </si>
@@ -75,163 +66,193 @@
     <t>Supplier Subtotal 1</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>CM5</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
+    <t>CWF-5</t>
+  </si>
+  <si>
+    <t>5-пиновый разъем с ключом</t>
+  </si>
+  <si>
+    <t>XP6</t>
+  </si>
+  <si>
+    <t>XT30PW-M</t>
+  </si>
+  <si>
+    <t>30 А (15 продолжительно), 2 контакта разъем угловой отец</t>
+  </si>
+  <si>
+    <t>XP8</t>
+  </si>
+  <si>
+    <t>LM5116MH</t>
+  </si>
+  <si>
+    <t>dc-dc понижающий adj 6-100v</t>
+  </si>
+  <si>
+    <t>DA1, DA1b</t>
+  </si>
+  <si>
+    <t>AP63200</t>
+  </si>
+  <si>
+    <t>DC-DC понижающий преобразователь, Vin: 3.8 - 40 В, adj, 2 А</t>
+  </si>
+  <si>
+    <t>DA2</t>
+  </si>
+  <si>
+    <t>DIN41612_48_3row_right_angle_male</t>
+  </si>
+  <si>
+    <t>DIN41612R (DS1120-48M0R13), Разъем (вилка) тип B 48pin (3х16), шаг 2.54мм трехрядный угловой (ряд АВC)</t>
+  </si>
+  <si>
+    <t>XP4</t>
+  </si>
+  <si>
+    <t>MAX485CSA</t>
+  </si>
+  <si>
+    <t>RS-485 приёмопередатчик</t>
+  </si>
+  <si>
+    <t>DD2</t>
+  </si>
+  <si>
+    <t>DF40C-40DS</t>
+  </si>
+  <si>
+    <t>Thruster control PCB</t>
+  </si>
+  <si>
+    <t>XP5</t>
+  </si>
+  <si>
+    <t>ES1D-E3/61T</t>
+  </si>
+  <si>
+    <t>Диод 1A 200V</t>
+  </si>
+  <si>
+    <t>VD1, VD1b</t>
+  </si>
+  <si>
+    <t>SP43-150K</t>
+  </si>
+  <si>
+    <t>Индуктивность на 15 мкГн, номинальный ток 1,3 А</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>CDSPRH127-150M</t>
+  </si>
+  <si>
+    <t>Индуктивность на 15 мкГн, номинальный ток 8,4 А</t>
+  </si>
+  <si>
+    <t>L1, L1b</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>Конденсатор</t>
+  </si>
+  <si>
+    <t>C1, C1b</t>
+  </si>
+  <si>
+    <t>C2, C2b</t>
+  </si>
+  <si>
+    <t>C3, C3b</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>C4, C4b, C25</t>
+  </si>
+  <si>
+    <t>C5, C5b</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>C6, C6b, C7, C7b, C9, C9b, C11, C11b, C13, C13b, C15, C15b, C17, C17b, C18, C18b, C20, C20b, C21, C21b, C22, C22b, C23, C23b, C27, C28</t>
+  </si>
+  <si>
+    <t>C8, C8b, C10, C10b, C12, C12b, C14, C14b</t>
+  </si>
+  <si>
+    <t>C16, C16b, C19, C19b</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>Конденсатор 0603C ёмкостью 0,1 мк 10%, 50 В, X7R</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>1-406541-5</t>
+  </si>
+  <si>
+    <t>Модульный разъем, Cat5, RJ45, Гнездо, 8 контакт(-ов), 8 вывод(-ов), 1 порт(-ов)</t>
+  </si>
+  <si>
+    <t>XP2</t>
+  </si>
+  <si>
+    <t>RPI</t>
+  </si>
+  <si>
+    <t>Одноплатный компьютер Raspberry PI 4B</t>
+  </si>
+  <si>
     <t>DD1</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Повышающий DC-DC преобразователь 2А 1.2МГц</t>
-  </si>
-  <si>
-    <t>DD2</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>RTL8367N-VB-CG</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>LM5116MHX/NOPB</t>
-  </si>
-  <si>
-    <t>6-100V Wide Vin, Current Mode Synchronous Buck Controller</t>
-  </si>
-  <si>
-    <t>U?</t>
-  </si>
-  <si>
-    <t>MSD-10-C</t>
-  </si>
-  <si>
-    <t>å¾®åž‹ SD å¡è¿žæŽ¥å™¨ï¼Œ 8 ä½ï¼Œ è¿žæŽ¥å™¨ï¼Œ é“°é“¾å¼ï¼Œ è¡¨é¢è´´è£…ï¼Œ æ¿ä¸Šæ–¹ 1.9 mm é«˜åº|ï¼Œ 15uâ€œé‡‘</t>
-  </si>
-  <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>DIN41612_32_2row_right_angle_father</t>
-  </si>
-  <si>
-    <t>DIN41612R (DS1118-32M0R23), Разъем (вилка) тип B 32pin (2х16), шаг 2.54мм двухрядный угловой (ряд АВ)</t>
-  </si>
-  <si>
-    <t>XP1</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>PCIe M2</t>
-  </si>
-  <si>
-    <t>PCIe M.2 Connectors, Storage and Server Connector, P=0.5mm, H=3.2mm, Key M,Gold Plating</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>USB_3.0</t>
-  </si>
-  <si>
-    <t>Двойной USB 3.0</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>B230A</t>
-  </si>
-  <si>
-    <t>Диод шоттки на 40 В, ном. ток 2.1 А</t>
-  </si>
-  <si>
-    <t>VD1</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>CDSPRH127-150M</t>
-  </si>
-  <si>
-    <t>Катушка индуктивности</t>
-  </si>
-  <si>
-    <t>L?</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>XTAL</t>
-  </si>
-  <si>
-    <t>Кварцевый резонатор</t>
-  </si>
-  <si>
-    <t>ZQ1</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Capacitor</t>
-  </si>
-  <si>
-    <t>Конденсатор</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>C3, C4</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>C?</t>
+    <t>Resistor</t>
+  </si>
+  <si>
+    <t>посадочное место 0603 под перемычку</t>
+  </si>
+  <si>
+    <t>R1, R1b</t>
+  </si>
+  <si>
+    <t>TC33X-2-503E</t>
+  </si>
+  <si>
+    <t>Потенциометр однооборотный керметный 50кОм 0.1Вт ±25% SMD лента на катушке</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>KK5045-04AG</t>
+  </si>
+  <si>
+    <t>Разъем типа провод-плата, 2.5 мм, 4 контакта</t>
+  </si>
+  <si>
+    <t>XP9</t>
   </si>
   <si>
     <t>21</t>
@@ -243,58 +264,133 @@
     <t>Разъем типа провод-плата, 3 мм, 2 контакт(-ов), Штыревой Разъем, Серия Micro-Fit для поверхностного монтажа</t>
   </si>
   <si>
-    <t>XP?</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Поменять футпринт на 1206</t>
-  </si>
-  <si>
-    <t>Резистор номиналом 9,1 Ом и точностью 1%</t>
-  </si>
-  <si>
-    <t>R?</t>
+    <t>XP1, XP3, XP7, XP10</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 1,5 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R10b</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 1,21 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 2,2 кОм 1%</t>
+  </si>
+  <si>
+    <t>R15, R16</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 2,7 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R3, R3b</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 3,9 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 4,7 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R9b</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 10 кОм 1%</t>
+  </si>
+  <si>
+    <t>R17</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>Resistor</t>
-  </si>
-  <si>
     <t>Резистор номиналом 10 кОм и точностью 1%</t>
   </si>
   <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Резистор номиналом 12 кОм и точностью 1%</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Резистор номиналом 31,6 кОм и точностью 1%</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>IHLP2525CZER4R7M01</t>
-  </si>
-  <si>
-    <t>ЧИП-индуктивность экранированная 4,7мкГн ±20% 5,5A 40мОм 2525</t>
-  </si>
-  <si>
-    <t>L1</t>
+    <t>R7, R7b</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 10 мОм, точностью 1%, 0.5Вт</t>
+  </si>
+  <si>
+    <t>R8, R8b</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 10,7 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 12,4 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R5, R5b</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 18 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 33 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R2, R2b</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 120 Ом и точностью 1%</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 180 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R4, R4b</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 470 кОм и точностью 1%</t>
+  </si>
+  <si>
+    <t>R6, R6b</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>Светодиод</t>
+  </si>
+  <si>
+    <t>HL1, HL2, HL3</t>
+  </si>
+  <si>
+    <t>SIR426DP-T1-GE3</t>
+  </si>
+  <si>
+    <t>Транзистор полевой MOSFET N-канальный 40В 41.7Вт</t>
+  </si>
+  <si>
+    <t>VT2, VT2b, VT3, VT3b</t>
+  </si>
+  <si>
+    <t>PDTC114ET</t>
+  </si>
+  <si>
+    <t>цифровой npn 50в 100мА</t>
+  </si>
+  <si>
+    <t>VT1, VT1b</t>
   </si>
 </sst>
 </file>
@@ -671,25 +767,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4E70E0-9023-41C7-8FCF-1E9654D57DAA}">
-  <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A9644F-36D0-4717-A8B8-483379B784D6}">
+  <dimension ref="A1:L47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" customWidth="1"/>
-    <col min="12" max="12" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="25.21875" customWidth="1"/>
+    <col min="8" max="8" width="22.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" customWidth="1"/>
+    <col min="10" max="10" width="21.33203125" customWidth="1"/>
+    <col min="11" max="11" width="19.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -727,7 +823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -751,15 +847,15 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>18</v>
@@ -775,21 +871,21 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -799,18 +895,18 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -823,16 +919,18 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -845,18 +943,18 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -869,18 +967,18 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -893,21 +991,21 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -917,18 +1015,18 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -941,21 +1039,21 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -965,21 +1063,21 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -989,21 +1087,21 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1013,21 +1111,21 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1037,21 +1135,21 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1061,21 +1159,21 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1085,21 +1183,21 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E17" s="1">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1109,21 +1207,21 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E18" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1133,21 +1231,21 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1157,18 +1255,18 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -1181,18 +1279,18 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -1205,18 +1303,16 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>79</v>
-      </c>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -1229,18 +1325,16 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>82</v>
-      </c>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -1253,8 +1347,582 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="1">
+        <v>4</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E45" s="1">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E46" s="1">
+        <v>4</v>
+      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>